--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486369_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486369_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.5643</v>
+        <v>3.651</v>
       </c>
       <c r="E2" t="n">
-        <v>1.9404</v>
+        <v>3.058</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6239</v>
+        <v>0.5931</v>
       </c>
       <c r="G2" t="n">
         <v>3.0896</v>
@@ -610,13 +610,13 @@
         <v>1.9576</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.7967</v>
+        <v>-0.7099</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.9589</v>
+        <v>0.1586</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.8377</v>
+        <v>-0.8685</v>
       </c>
       <c r="V2" t="n">
         <v>-0.6863</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1929</v>
+        <v>1.268</v>
       </c>
       <c r="E3" t="n">
-        <v>1.471</v>
+        <v>0.5769</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7219</v>
+        <v>0.6911</v>
       </c>
       <c r="G3" t="n">
         <v>0.1781</v>
@@ -688,13 +688,13 @@
         <v>2.3926</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8735000000000001</v>
+        <v>-0.0514</v>
       </c>
       <c r="T3" t="n">
-        <v>1.6992</v>
+        <v>0.8051</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.8257</v>
+        <v>-0.8565</v>
       </c>
       <c r="V3" t="n">
         <v>-1.2512</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>V. FAVERANI TATSCH</t>
+          <t>M. AYESA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3548</v>
+        <v>1.2285</v>
       </c>
       <c r="E4" t="n">
-        <v>2.7519</v>
+        <v>1.7643</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.3971</v>
+        <v>-0.5359</v>
       </c>
       <c r="G4" t="n">
-        <v>-2.4795</v>
+        <v>0.9797</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.0101</v>
+        <v>0.6538</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4693</v>
+        <v>0.3259</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.2623</v>
+        <v>2.1321</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.5134</v>
+        <v>0.6387</v>
       </c>
       <c r="L4" t="n">
-        <v>0.251</v>
+        <v>1.4933</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.2171</v>
+        <v>-1.1523</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.4967</v>
+        <v>0.0151</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.7204</v>
+        <v>-1.1674</v>
       </c>
       <c r="P4" t="n">
-        <v>1.0875</v>
+        <v>1.305</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.0875</v>
+        <v>1.305</v>
       </c>
       <c r="S4" t="n">
-        <v>1.6168</v>
+        <v>-1.0563</v>
       </c>
       <c r="T4" t="n">
-        <v>1.8843</v>
+        <v>-0.3677</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2675</v>
+        <v>-0.6886</v>
       </c>
       <c r="V4" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. AYESA RODRIGUEZ</t>
+          <t>J. DAVIS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9933999999999999</v>
+        <v>0.3757</v>
       </c>
       <c r="E5" t="n">
-        <v>1.6526</v>
+        <v>-1.6231</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.6592</v>
+        <v>1.9988</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9797</v>
+        <v>-0.528</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6538</v>
+        <v>-2.4086</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3259</v>
+        <v>1.8806</v>
       </c>
       <c r="J5" t="n">
-        <v>2.1321</v>
+        <v>-2.1925</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6387</v>
+        <v>-2.1558</v>
       </c>
       <c r="L5" t="n">
-        <v>1.4933</v>
+        <v>-0.0366</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.1523</v>
+        <v>1.6644</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0151</v>
+        <v>-0.2528</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.1674</v>
+        <v>1.9172</v>
       </c>
       <c r="P5" t="n">
-        <v>1.305</v>
+        <v>1.9576</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R5" t="n">
-        <v>1.305</v>
+        <v>3.0451</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.2913</v>
+        <v>-1.1278</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4795</v>
+        <v>0.3317</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.8119</v>
+        <v>-1.4595</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.074</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.3252</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.2512</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. HARGUINDEY MANEIRO</t>
+          <t>A. GARUBA ALARI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7398</v>
+        <v>-0.227</v>
       </c>
       <c r="E6" t="n">
-        <v>2.5596</v>
+        <v>-1.1511</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.8198</v>
+        <v>0.9241</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.5878</v>
+        <v>-1.1644</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.7543</v>
+        <v>-1.2226</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8335</v>
+        <v>0.0582</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.052</v>
+        <v>-1.758</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0611</v>
+        <v>-1.4536</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.1131</v>
+        <v>-0.3044</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.5357</v>
+        <v>0.5936</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8153</v>
+        <v>0.2311</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.7204</v>
+        <v>0.3626</v>
       </c>
       <c r="P6" t="n">
-        <v>1.5225</v>
+        <v>0.435</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5225</v>
+        <v>0.435</v>
       </c>
       <c r="S6" t="n">
-        <v>0.805</v>
+        <v>0.5023</v>
       </c>
       <c r="T6" t="n">
-        <v>1.4817</v>
+        <v>0.6069</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6767</v>
+        <v>-0.1046</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. GARUBA ALARI</t>
+          <t>A. HARGUINDEY MANEIRO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0151</v>
+        <v>-0.4086</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.8158</v>
+        <v>1.442</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8008</v>
+        <v>-1.8507</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.1644</v>
+        <v>-1.5878</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.2226</v>
+        <v>-0.7543</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0582</v>
+        <v>-0.8335</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.758</v>
+        <v>-0.052</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.4536</v>
+        <v>0.0611</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.3044</v>
+        <v>-0.1131</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5936</v>
+        <v>-1.5357</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2311</v>
+        <v>-0.8153</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3626</v>
+        <v>-0.7204</v>
       </c>
       <c r="P7" t="n">
-        <v>0.435</v>
+        <v>1.5225</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.435</v>
+        <v>1.5225</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7143</v>
+        <v>-0.3434</v>
       </c>
       <c r="T7" t="n">
-        <v>0.9421</v>
+        <v>0.3641</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2278</v>
+        <v>-0.7075</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4025</v>
+        <v>-0.4371</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.4295</v>
+        <v>-1.0943</v>
       </c>
       <c r="F8" t="n">
-        <v>1.027</v>
+        <v>0.6572</v>
       </c>
       <c r="G8" t="n">
         <v>-1.0599</v>
@@ -1078,13 +1078,13 @@
         <v>1.9576</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5242</v>
+        <v>-0.5588</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1406</v>
+        <v>0.4759</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6647999999999999</v>
+        <v>-1.0347</v>
       </c>
       <c r="V8" t="n">
         <v>1.3991</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. DAVIS</t>
+          <t>V. FAVERANI TATSCH</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.6031</v>
+        <v>-0.4795</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.2937</v>
+        <v>1.4108</v>
       </c>
       <c r="F9" t="n">
-        <v>1.6906</v>
+        <v>-1.8903</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.528</v>
+        <v>-2.4795</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.4086</v>
+        <v>-2.0101</v>
       </c>
       <c r="I9" t="n">
-        <v>1.8806</v>
+        <v>-0.4693</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.1925</v>
+        <v>-0.2623</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.1558</v>
+        <v>-0.5134</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.0366</v>
+        <v>0.251</v>
       </c>
       <c r="M9" t="n">
-        <v>1.6644</v>
+        <v>-2.2171</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2528</v>
+        <v>-1.4967</v>
       </c>
       <c r="O9" t="n">
-        <v>1.9172</v>
+        <v>-0.7204</v>
       </c>
       <c r="P9" t="n">
-        <v>1.9576</v>
+        <v>1.0875</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>3.0451</v>
+        <v>1.0875</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.1066</v>
+        <v>-0.2175</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3389</v>
+        <v>0.5432</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.7677</v>
+        <v>-0.7607</v>
       </c>
       <c r="V9" t="n">
-        <v>0.074</v>
+        <v>1.13</v>
       </c>
       <c r="W9" t="n">
-        <v>1.3252</v>
+        <v>1.13</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2512</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>I. RIVERA CARROLL</t>
+          <t>K. WEBSTER</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.1644</v>
+        <v>-0.5949</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.492</v>
+        <v>1.035</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6724</v>
+        <v>-1.6298</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.1938</v>
+        <v>0.6515</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.244</v>
+        <v>0.0881</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0502</v>
+        <v>0.5634</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.0605</v>
+        <v>2.2366</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1674</v>
+        <v>1.3354</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.2279</v>
+        <v>0.9013</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.1333</v>
+        <v>-1.5852</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.4114</v>
+        <v>-1.2473</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2781</v>
+        <v>-0.3379</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.2175</v>
+        <v>0.435</v>
       </c>
       <c r="Q10" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R10" t="n">
-        <v>0.87</v>
+        <v>1.5225</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2175</v>
+        <v>-1.2909</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2656</v>
+        <v>-0.1142</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4831</v>
+        <v>-1.1768</v>
       </c>
       <c r="V10" t="n">
-        <v>0.4644</v>
+        <v>-0.3904</v>
       </c>
       <c r="W10" t="n">
-        <v>0.3904</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.074</v>
+        <v>-0.3904</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>K. WEBSTER</t>
+          <t>I. RIVERA CARROLL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.4311</v>
+        <v>-1.0526</v>
       </c>
       <c r="E11" t="n">
-        <v>0.4762</v>
+        <v>-0.3802</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.9073</v>
+        <v>-0.6724</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6515</v>
+        <v>-1.1938</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0881</v>
+        <v>-1.244</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5634</v>
+        <v>0.0502</v>
       </c>
       <c r="J11" t="n">
-        <v>2.2366</v>
+        <v>-0.0605</v>
       </c>
       <c r="K11" t="n">
-        <v>1.3354</v>
+        <v>0.1674</v>
       </c>
       <c r="L11" t="n">
-        <v>0.9013</v>
+        <v>-0.2279</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.5852</v>
+        <v>-1.1333</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.2473</v>
+        <v>-1.4114</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.3379</v>
+        <v>0.2781</v>
       </c>
       <c r="P11" t="n">
-        <v>0.435</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q11" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5225</v>
+        <v>0.87</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.1271</v>
+        <v>-0.1057</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6729000000000001</v>
+        <v>0.3773</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.4542</v>
+        <v>-0.4831</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.3904</v>
+        <v>0.4644</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.3904</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.3904</v>
+        <v>0.074</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.8352</v>
+        <v>-1.5808</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.3433</v>
+        <v>-1.1198</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.4919</v>
+        <v>-0.4611</v>
       </c>
       <c r="G12" t="n">
         <v>-0.4822</v>
@@ -1390,13 +1390,13 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2655</v>
+        <v>-0.0111</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.274</v>
+        <v>-0.0505</v>
       </c>
       <c r="U12" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.0394</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.4847</v>
+        <v>-6.8335</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.4864</v>
+        <v>-1.9276</v>
       </c>
       <c r="F13" t="n">
-        <v>-4.9983</v>
+        <v>-4.9058</v>
       </c>
       <c r="G13" t="n">
         <v>0.2215</v>
@@ -1468,13 +1468,13 @@
         <v>1.305</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.206</v>
+        <v>-1.5547</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6729000000000001</v>
+        <v>-0.1142</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.533</v>
+        <v>-1.4405</v>
       </c>
       <c r="V13" t="n">
         <v>-2.4552</v>
@@ -1501,22 +1501,22 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-5.0909</v>
+        <v>-5.090800000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>1.991000000000001</v>
+        <v>1.9909</v>
       </c>
       <c r="F14" t="n">
-        <v>-7.0818</v>
+        <v>-7.081700000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>-3.375200000000001</v>
+        <v>-3.3752</v>
       </c>
       <c r="H14" t="n">
         <v>-9.534899999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>6.1597</v>
+        <v>6.159700000000002</v>
       </c>
       <c r="J14" t="n">
         <v>2.8541</v>
@@ -1528,10 +1528,10 @@
         <v>3.9008</v>
       </c>
       <c r="M14" t="n">
-        <v>-6.2292</v>
+        <v>-6.229200000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>-8.488200000000001</v>
+        <v>-8.488199999999999</v>
       </c>
       <c r="O14" t="n">
         <v>2.2589</v>
@@ -1546,13 +1546,13 @@
         <v>17.4004</v>
       </c>
       <c r="S14" t="n">
-        <v>-6.5253</v>
+        <v>-6.5252</v>
       </c>
       <c r="T14" t="n">
-        <v>3.016399999999999</v>
+        <v>3.0162</v>
       </c>
       <c r="U14" t="n">
-        <v>-9.541600000000001</v>
+        <v>-9.541599999999999</v>
       </c>
       <c r="V14" t="n">
         <v>-1.7156</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.4553</v>
+        <v>5.9166</v>
       </c>
       <c r="E15" t="n">
-        <v>5.675</v>
+        <v>6.2338</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.2197</v>
+        <v>-0.3172</v>
       </c>
       <c r="G15" t="n">
         <v>3.7483</v>
@@ -1624,13 +1624,13 @@
         <v>1.5225</v>
       </c>
       <c r="S15" t="n">
-        <v>0.142</v>
+        <v>0.6032</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1694</v>
+        <v>0.3894</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3115</v>
+        <v>0.2139</v>
       </c>
       <c r="V15" t="n">
         <v>1.13</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>I. DIOP GAYE</t>
+          <t>P. JORGENSEN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.8375</v>
+        <v>4.9927</v>
       </c>
       <c r="E16" t="n">
-        <v>4.6619</v>
+        <v>5.9396</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1756</v>
+        <v>-0.9469</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.1502</v>
+        <v>4.6695</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8547</v>
+        <v>1.5331</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.0049</v>
+        <v>3.1364</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.6375999999999999</v>
+        <v>5.7981</v>
       </c>
       <c r="K16" t="n">
-        <v>0.776</v>
+        <v>1.4544</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.4136</v>
+        <v>4.3437</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.5125999999999999</v>
+        <v>-1.1285</v>
       </c>
       <c r="N16" t="n">
         <v>0.07870000000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.5913</v>
+        <v>-1.2073</v>
       </c>
       <c r="P16" t="n">
-        <v>0.87</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R16" t="n">
-        <v>0.87</v>
+        <v>1.9576</v>
       </c>
       <c r="S16" t="n">
-        <v>5.1177</v>
+        <v>0.3455</v>
       </c>
       <c r="T16" t="n">
-        <v>5.2995</v>
+        <v>0.9913999999999999</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1818</v>
+        <v>-0.6459</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.3252</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. BARRO</t>
+          <t>G. JOU COLL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.4436</v>
+        <v>3.2105</v>
       </c>
       <c r="E17" t="n">
-        <v>3.8831</v>
+        <v>1.4649</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4395</v>
+        <v>1.7456</v>
       </c>
       <c r="G17" t="n">
-        <v>1.8665</v>
+        <v>-1.3183</v>
       </c>
       <c r="H17" t="n">
-        <v>2.418</v>
+        <v>0.9304</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.5514</v>
+        <v>-2.2487</v>
       </c>
       <c r="J17" t="n">
-        <v>1.3933</v>
+        <v>-0.9062</v>
       </c>
       <c r="K17" t="n">
-        <v>2.1383</v>
+        <v>0.6022</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.7451</v>
+        <v>-1.5084</v>
       </c>
       <c r="M17" t="n">
-        <v>0.4732</v>
+        <v>-0.4121</v>
       </c>
       <c r="N17" t="n">
-        <v>0.2796</v>
+        <v>0.3282</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1936</v>
+        <v>-0.7403</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.6525</v>
+        <v>0.6525</v>
       </c>
       <c r="Q17" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R17" t="n">
-        <v>0.435</v>
+        <v>1.7401</v>
       </c>
       <c r="S17" t="n">
-        <v>1.4694</v>
+        <v>1.8116</v>
       </c>
       <c r="T17" t="n">
-        <v>1.6872</v>
+        <v>1.0034</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2178</v>
+        <v>0.8081</v>
       </c>
       <c r="V17" t="n">
-        <v>0.7602</v>
+        <v>2.0647</v>
       </c>
       <c r="W17" t="n">
-        <v>1.8902</v>
+        <v>2.4552</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.13</v>
+        <v>-0.3904</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. JORGENSEN</t>
+          <t>S. BARRO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.4295</v>
+        <v>2.4032</v>
       </c>
       <c r="E18" t="n">
-        <v>4.7103</v>
+        <v>3.2126</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.2808</v>
+        <v>-0.8094</v>
       </c>
       <c r="G18" t="n">
-        <v>4.6695</v>
+        <v>1.8665</v>
       </c>
       <c r="H18" t="n">
-        <v>1.5331</v>
+        <v>2.418</v>
       </c>
       <c r="I18" t="n">
-        <v>3.1364</v>
+        <v>-0.5514</v>
       </c>
       <c r="J18" t="n">
-        <v>5.7981</v>
+        <v>1.3933</v>
       </c>
       <c r="K18" t="n">
-        <v>1.4544</v>
+        <v>2.1383</v>
       </c>
       <c r="L18" t="n">
-        <v>4.3437</v>
+        <v>-0.7451</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.1285</v>
+        <v>0.4732</v>
       </c>
       <c r="N18" t="n">
-        <v>0.07870000000000001</v>
+        <v>0.2796</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.2073</v>
+        <v>0.1936</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.2175</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R18" t="n">
-        <v>1.9576</v>
+        <v>0.435</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.2178</v>
+        <v>0.429</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2379</v>
+        <v>1.0166</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.9799</v>
+        <v>-0.5876</v>
       </c>
       <c r="V18" t="n">
-        <v>0.1952</v>
+        <v>0.7602</v>
       </c>
       <c r="W18" t="n">
-        <v>1.3252</v>
+        <v>1.8902</v>
       </c>
       <c r="X18" t="n">
         <v>-1.13</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>G. JOU COLL</t>
+          <t>I. DIOP GAYE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>3.3582</v>
+        <v>1.6158</v>
       </c>
       <c r="E19" t="n">
-        <v>1.5766</v>
+        <v>1.5326</v>
       </c>
       <c r="F19" t="n">
-        <v>1.7815</v>
+        <v>0.0832</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.3183</v>
+        <v>-1.1502</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9304</v>
+        <v>0.8547</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.2487</v>
+        <v>-2.0049</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.9062</v>
+        <v>-0.6375999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6022</v>
+        <v>0.776</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.5084</v>
+        <v>-1.4136</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.4121</v>
+        <v>-0.5125999999999999</v>
       </c>
       <c r="N19" t="n">
-        <v>0.3282</v>
+        <v>0.07870000000000001</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.7403</v>
+        <v>-0.5913</v>
       </c>
       <c r="P19" t="n">
-        <v>0.6525</v>
+        <v>0.87</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.7401</v>
+        <v>0.87</v>
       </c>
       <c r="S19" t="n">
-        <v>1.9592</v>
+        <v>1.896</v>
       </c>
       <c r="T19" t="n">
-        <v>1.1152</v>
+        <v>2.1703</v>
       </c>
       <c r="U19" t="n">
-        <v>0.8441</v>
+        <v>-0.2743</v>
       </c>
       <c r="V19" t="n">
-        <v>2.0647</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>2.4552</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.3904</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. CREMO</t>
+          <t>C. DE SOUZA PACHECO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.7732</v>
+        <v>0.1121</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.4539</v>
+        <v>2.3686</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6807</v>
+        <v>-2.2564</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.9633</v>
+        <v>1.2927</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1642</v>
+        <v>0.2982</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.1275</v>
+        <v>0.9945000000000001</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.3409</v>
+        <v>2.2857</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1492</v>
+        <v>0.849</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.4901</v>
+        <v>1.4368</v>
       </c>
       <c r="M20" t="n">
-        <v>0.3776</v>
+        <v>-0.9931</v>
       </c>
       <c r="N20" t="n">
-        <v>0.0151</v>
+        <v>-0.5508</v>
       </c>
       <c r="O20" t="n">
-        <v>0.3626</v>
+        <v>-0.4423</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2175</v>
+        <v>0.87</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R20" t="n">
-        <v>0.2175</v>
+        <v>1.9576</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0274</v>
+        <v>0.2094</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.113</v>
+        <v>0.7799</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0856</v>
+        <v>-0.5705</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-2.2599</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.3904</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-2.6504</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>C. DE SOUZA PACHECO</t>
+          <t>J. CREMO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.058</v>
+        <v>-0.1528</v>
       </c>
       <c r="E21" t="n">
-        <v>1.8098</v>
+        <v>-0.8951</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.8678</v>
+        <v>0.7423999999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>1.2927</v>
+        <v>-0.9633</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2982</v>
+        <v>0.1642</v>
       </c>
       <c r="I21" t="n">
-        <v>0.9945000000000001</v>
+        <v>-1.1275</v>
       </c>
       <c r="J21" t="n">
-        <v>2.2857</v>
+        <v>-1.3409</v>
       </c>
       <c r="K21" t="n">
-        <v>0.849</v>
+        <v>0.1492</v>
       </c>
       <c r="L21" t="n">
-        <v>1.4368</v>
+        <v>-1.4901</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.9931</v>
+        <v>0.3776</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5508</v>
+        <v>0.0151</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.4423</v>
+        <v>0.3626</v>
       </c>
       <c r="P21" t="n">
-        <v>0.87</v>
+        <v>0.2175</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.9576</v>
+        <v>0.2175</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.9608</v>
+        <v>0.593</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2211</v>
+        <v>0.4458</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.1819</v>
+        <v>0.1472</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.2599</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0.3904</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.6504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.1079</v>
+        <v>-2.1824</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.8712</v>
+        <v>-3.0947</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7633</v>
+        <v>0.9123</v>
       </c>
       <c r="G22" t="n">
         <v>0.2042</v>
@@ -2170,13 +2170,13 @@
         <v>1.5225</v>
       </c>
       <c r="S22" t="n">
-        <v>1.6031</v>
+        <v>1.5286</v>
       </c>
       <c r="T22" t="n">
-        <v>1.6187</v>
+        <v>1.3952</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0156</v>
+        <v>0.1334</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.0287</v>
+        <v>-2.8746</v>
       </c>
       <c r="E23" t="n">
         <v>-1.4356</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.5931</v>
+        <v>-1.439</v>
       </c>
       <c r="G23" t="n">
         <v>-1.4719</v>
@@ -2248,13 +2248,13 @@
         <v>0.2175</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6868</v>
+        <v>-0.5327</v>
       </c>
       <c r="T23" t="n">
         <v>0.7006</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.3874</v>
+        <v>-1.2332</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-8.4656</v>
+        <v>-7.2054</v>
       </c>
       <c r="E24" t="n">
-        <v>-9.474299999999999</v>
+        <v>-8.244999999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>1.0088</v>
+        <v>1.0396</v>
       </c>
       <c r="G24" t="n">
         <v>-3.5024</v>
@@ -2326,13 +2326,13 @@
         <v>0.435</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.8735000000000001</v>
+        <v>0.3866</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5804</v>
+        <v>0.6489</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2931</v>
+        <v>-0.2623</v>
       </c>
       <c r="V24" t="n">
         <v>-0.1745</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>5.0907</v>
+        <v>5.8357</v>
       </c>
       <c r="E25" t="n">
-        <v>7.081700000000001</v>
+        <v>7.081700000000003</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.991</v>
+        <v>-1.2458</v>
       </c>
       <c r="G25" t="n">
         <v>3.375099999999999</v>
@@ -2377,7 +2377,7 @@
         <v>-6.159599999999999</v>
       </c>
       <c r="J25" t="n">
-        <v>6.229400000000001</v>
+        <v>6.229399999999999</v>
       </c>
       <c r="K25" t="n">
         <v>8.488199999999999</v>
@@ -2404,13 +2404,13 @@
         <v>10.8753</v>
       </c>
       <c r="S25" t="n">
-        <v>6.5251</v>
+        <v>7.2702</v>
       </c>
       <c r="T25" t="n">
-        <v>9.541599999999999</v>
+        <v>9.541499999999999</v>
       </c>
       <c r="U25" t="n">
-        <v>-3.0163</v>
+        <v>-2.2712</v>
       </c>
       <c r="V25" t="n">
         <v>1.7157</v>
